--- a/data/externalStats/File1/RPT_RPT7043243328387RJ_externalStats.xlsx
+++ b/data/externalStats/File1/RPT_RPT7043243328387RJ_externalStats.xlsx
@@ -3905,10 +3905,10 @@
         <v>13</v>
       </c>
       <c r="J53" s="127" t="n">
-        <v>3.367208266425485</v>
+        <v>3.367208266425486</v>
       </c>
       <c r="K53" s="128" t="n">
-        <v>2.526596826732871</v>
+        <v>2.52659682673287</v>
       </c>
       <c r="L53" s="128" t="n">
         <v>5.050972602908543</v>
@@ -3926,7 +3926,7 @@
         <v>2.389684032962864</v>
       </c>
       <c r="R53" s="128" t="n">
-        <v>4.691096276623046</v>
+        <v>4.691096276623045</v>
       </c>
       <c r="S53" s="128" t="n">
         <v>0</v>
@@ -3947,7 +3947,7 @@
         <v>0</v>
       </c>
       <c r="Z53" s="129" t="n">
-        <v>9.726130306163938</v>
+        <v>9.726130306163936</v>
       </c>
       <c r="AE53" s="121" t="n">
         <v>5</v>
@@ -4067,7 +4067,7 @@
         <v>11</v>
       </c>
       <c r="J55" s="130" t="n">
-        <v>11.00421963992369</v>
+        <v>11.0042196399237</v>
       </c>
       <c r="K55" s="131" t="n">
         <v>0</v>
@@ -4079,7 +4079,7 @@
         <v>0</v>
       </c>
       <c r="N55" s="132" t="n">
-        <v>11.00421963992369</v>
+        <v>11.0042196399237</v>
       </c>
       <c r="P55" s="130" t="n">
         <v>11.25327823035992</v>
@@ -4097,7 +4097,7 @@
         <v>11.25327823035992</v>
       </c>
       <c r="V55" s="130" t="n">
-        <v>11.64231197178806</v>
+        <v>11.64231197178807</v>
       </c>
       <c r="W55" s="131" t="n">
         <v>0</v>
@@ -4109,7 +4109,7 @@
         <v>0</v>
       </c>
       <c r="Z55" s="132" t="n">
-        <v>11.64231197178806</v>
+        <v>11.64231197178807</v>
       </c>
       <c r="AE55" s="121" t="n">
         <v>7</v>
@@ -4232,10 +4232,10 @@
         <v>63.51701400863278</v>
       </c>
       <c r="K57" s="131" t="n">
-        <v>55.26075949714093</v>
+        <v>55.26075949714092</v>
       </c>
       <c r="L57" s="131" t="n">
-        <v>70.05762760070748</v>
+        <v>70.05762760070749</v>
       </c>
       <c r="M57" s="131" t="n">
         <v>0</v>
@@ -4244,13 +4244,13 @@
         <v>188.8354011064812</v>
       </c>
       <c r="P57" s="130" t="n">
-        <v>62.84620709537453</v>
+        <v>62.84620709537454</v>
       </c>
       <c r="Q57" s="131" t="n">
         <v>53.99726869828643</v>
       </c>
       <c r="R57" s="131" t="n">
-        <v>67.54614245337035</v>
+        <v>67.54614245337034</v>
       </c>
       <c r="S57" s="131" t="n">
         <v>0</v>
@@ -4265,7 +4265,7 @@
         <v>54.54301454127602</v>
       </c>
       <c r="X57" s="131" t="n">
-        <v>66.06395772949691</v>
+        <v>66.06395772949689</v>
       </c>
       <c r="Y57" s="131" t="n">
         <v>0</v>
@@ -4553,7 +4553,7 @@
         <v>72</v>
       </c>
       <c r="J61" s="130" t="n">
-        <v>33.80888039188297</v>
+        <v>33.80888039188298</v>
       </c>
       <c r="K61" s="131" t="n">
         <v>11.56721622874408</v>
@@ -4565,10 +4565,10 @@
         <v>0</v>
       </c>
       <c r="N61" s="132" t="n">
-        <v>72.42718278064054</v>
+        <v>72.42718278064055</v>
       </c>
       <c r="P61" s="130" t="n">
-        <v>34.38023379828336</v>
+        <v>34.38023379828337</v>
       </c>
       <c r="Q61" s="131" t="n">
         <v>11.88171813551708</v>
@@ -4589,7 +4589,7 @@
         <v>12.10617120330805</v>
       </c>
       <c r="X61" s="131" t="n">
-        <v>25.76138345852207</v>
+        <v>25.76138345852206</v>
       </c>
       <c r="Y61" s="131" t="n">
         <v>0</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="AG62" s="122" t="n">
-        <v>1561.471198555859</v>
+        <v>1561.47119855586</v>
       </c>
       <c r="AH62" s="56" t="n">
         <v>7.487248693337843</v>
@@ -4718,10 +4718,10 @@
         <v>2.58953491341282</v>
       </c>
       <c r="K63" s="131" t="n">
-        <v>0.4725356733129047</v>
+        <v>0.4725356733129189</v>
       </c>
       <c r="L63" s="131" t="n">
-        <v>0.2078802046455763</v>
+        <v>0.2078802046455621</v>
       </c>
       <c r="M63" s="131" t="n">
         <v>7.308333158315506</v>
@@ -4730,34 +4730,34 @@
         <v>10.57828394968681</v>
       </c>
       <c r="P63" s="130" t="n">
-        <v>2.085521369386882</v>
+        <v>2.085521369386896</v>
       </c>
       <c r="Q63" s="131" t="n">
-        <v>0.1405100237658843</v>
+        <v>0.1405100237658985</v>
       </c>
       <c r="R63" s="131" t="n">
-        <v>0.08133752942403305</v>
+        <v>0.08133752942404726</v>
       </c>
       <c r="S63" s="131" t="n">
         <v>6.991768917026942</v>
       </c>
       <c r="T63" s="132" t="n">
-        <v>9.299137839603741</v>
+        <v>9.299137839603784</v>
       </c>
       <c r="V63" s="130" t="n">
-        <v>1.437311782396435</v>
+        <v>1.437311782396449</v>
       </c>
       <c r="W63" s="131" t="n">
         <v>0.1196840743637324</v>
       </c>
       <c r="X63" s="131" t="n">
-        <v>0.07925896025578538</v>
+        <v>0.0792589602558138</v>
       </c>
       <c r="Y63" s="131" t="n">
-        <v>6.012182320226879</v>
+        <v>6.012182320226881</v>
       </c>
       <c r="Z63" s="132" t="n">
-        <v>7.648437137242832</v>
+        <v>7.648437137242876</v>
       </c>
       <c r="AE63" s="121" t="n">
         <v>15</v>
@@ -4820,10 +4820,10 @@
         <v>0</v>
       </c>
       <c r="S64" s="134" t="n">
-        <v>6.877622740410127</v>
+        <v>6.877622740410126</v>
       </c>
       <c r="T64" s="135" t="n">
-        <v>6.877622740410127</v>
+        <v>6.877622740410126</v>
       </c>
       <c r="V64" s="133" t="n">
         <v>0</v>
@@ -4835,10 +4835,10 @@
         <v>0</v>
       </c>
       <c r="Y64" s="134" t="n">
-        <v>5.894981001423755</v>
+        <v>5.894981001423756</v>
       </c>
       <c r="Z64" s="135" t="n">
-        <v>5.894981001423755</v>
+        <v>5.894981001423756</v>
       </c>
       <c r="AE64" s="121" t="n">
         <v>16</v>
@@ -5045,10 +5045,10 @@
         <v>0</v>
       </c>
       <c r="J67" s="139" t="n">
-        <v>2.893467696716072</v>
+        <v>2.893467696716073</v>
       </c>
       <c r="K67" s="140" t="n">
-        <v>3.224075867332796</v>
+        <v>3.224075867332795</v>
       </c>
       <c r="L67" s="140" t="n">
         <v>5.423006045073501</v>
@@ -5060,10 +5060,10 @@
         <v>14.94042145573816</v>
       </c>
       <c r="P67" s="139" t="n">
-        <v>5.575560697241529</v>
+        <v>5.575560697241528</v>
       </c>
       <c r="Q67" s="140" t="n">
-        <v>4.527875195047197</v>
+        <v>4.527875195047198</v>
       </c>
       <c r="R67" s="140" t="n">
         <v>5.836822602345891</v>
@@ -5075,7 +5075,7 @@
         <v>19.39887874626104</v>
       </c>
       <c r="V67" s="139" t="n">
-        <v>9.739762734353809</v>
+        <v>9.73976273435381</v>
       </c>
       <c r="W67" s="140" t="n">
         <v>5.762176317484299</v>
@@ -5168,7 +5168,7 @@
         <v>21.71266355619796</v>
       </c>
       <c r="Z68" s="144" t="n">
-        <v>326.3064173993097</v>
+        <v>326.3064173993098</v>
       </c>
       <c r="AE68" s="124" t="n">
         <v>20</v>
@@ -6357,7 +6357,7 @@
         <v>5.381189522398397</v>
       </c>
       <c r="N86" s="144" t="n">
-        <v>65.89275335765966</v>
+        <v>65.89275335765964</v>
       </c>
       <c r="P86" s="142" t="n">
         <v>53.95276536276727</v>
@@ -6541,10 +6541,10 @@
         <v>13</v>
       </c>
       <c r="J89" s="127" t="n">
-        <v>3.367208266425485</v>
+        <v>3.367208266425486</v>
       </c>
       <c r="K89" s="128" t="n">
-        <v>2.526596826732871</v>
+        <v>2.52659682673287</v>
       </c>
       <c r="L89" s="128" t="n">
         <v>5.050972602908543</v>
@@ -6562,7 +6562,7 @@
         <v>2.389684032962864</v>
       </c>
       <c r="R89" s="128" t="n">
-        <v>4.691096276623046</v>
+        <v>4.691096276623045</v>
       </c>
       <c r="S89" s="128" t="n">
         <v>0</v>
@@ -6583,7 +6583,7 @@
         <v>0</v>
       </c>
       <c r="Z89" s="129" t="n">
-        <v>9.726130306163938</v>
+        <v>9.726130306163936</v>
       </c>
     </row>
     <row r="90">
@@ -6675,7 +6675,7 @@
         <v>11</v>
       </c>
       <c r="J91" s="130" t="n">
-        <v>11.00421963992369</v>
+        <v>11.0042196399237</v>
       </c>
       <c r="K91" s="131" t="n">
         <v>0</v>
@@ -6687,7 +6687,7 @@
         <v>0</v>
       </c>
       <c r="N91" s="132" t="n">
-        <v>11.00421963992369</v>
+        <v>11.0042196399237</v>
       </c>
       <c r="P91" s="130" t="n">
         <v>11.25327823035992</v>
@@ -6705,7 +6705,7 @@
         <v>11.25327823035992</v>
       </c>
       <c r="V91" s="130" t="n">
-        <v>11.64231197178806</v>
+        <v>11.64231197178807</v>
       </c>
       <c r="W91" s="131" t="n">
         <v>0</v>
@@ -6717,7 +6717,7 @@
         <v>0</v>
       </c>
       <c r="Z91" s="132" t="n">
-        <v>11.64231197178806</v>
+        <v>11.64231197178807</v>
       </c>
     </row>
     <row r="92">
@@ -6812,10 +6812,10 @@
         <v>67.61543233395422</v>
       </c>
       <c r="K93" s="131" t="n">
-        <v>70.04432412598567</v>
+        <v>70.04432412598565</v>
       </c>
       <c r="L93" s="131" t="n">
-        <v>83.67502034869864</v>
+        <v>83.67502034869865</v>
       </c>
       <c r="M93" s="131" t="n">
         <v>0</v>
@@ -6824,13 +6824,13 @@
         <v>221.3347768086385</v>
       </c>
       <c r="P93" s="130" t="n">
-        <v>68.90194032977443</v>
+        <v>68.90194032977445</v>
       </c>
       <c r="Q93" s="131" t="n">
-        <v>72.96124159975149</v>
+        <v>72.96124159975147</v>
       </c>
       <c r="R93" s="131" t="n">
-        <v>83.61706243415738</v>
+        <v>83.61706243415736</v>
       </c>
       <c r="S93" s="131" t="n">
         <v>0</v>
@@ -6845,7 +6845,7 @@
         <v>75.74904598402861</v>
       </c>
       <c r="X93" s="131" t="n">
-        <v>84.21330605471455</v>
+        <v>84.21330605471454</v>
       </c>
       <c r="Y93" s="131" t="n">
         <v>0</v>
@@ -7077,7 +7077,7 @@
         <v>72</v>
       </c>
       <c r="J97" s="130" t="n">
-        <v>33.80888039188297</v>
+        <v>33.80888039188298</v>
       </c>
       <c r="K97" s="131" t="n">
         <v>11.56721622874408</v>
@@ -7089,10 +7089,10 @@
         <v>0</v>
       </c>
       <c r="N97" s="132" t="n">
-        <v>72.42718278064054</v>
+        <v>72.42718278064055</v>
       </c>
       <c r="P97" s="130" t="n">
-        <v>34.38023379828336</v>
+        <v>34.38023379828337</v>
       </c>
       <c r="Q97" s="131" t="n">
         <v>11.88171813551708</v>
@@ -7113,13 +7113,13 @@
         <v>12.10617120330805</v>
       </c>
       <c r="X97" s="131" t="n">
-        <v>28.98737431110368</v>
+        <v>28.98737431110367</v>
       </c>
       <c r="Y97" s="131" t="n">
         <v>0</v>
       </c>
       <c r="Z97" s="132" t="n">
-        <v>76.5085550051911</v>
+        <v>76.50855500519108</v>
       </c>
     </row>
     <row r="98">
@@ -7211,22 +7211,22 @@
         <v>9</v>
       </c>
       <c r="J99" s="130" t="n">
-        <v>2.589534913412791</v>
+        <v>2.58953491341282</v>
       </c>
       <c r="K99" s="131" t="n">
-        <v>0.4725356733129047</v>
+        <v>0.4725356733129331</v>
       </c>
       <c r="L99" s="131" t="n">
-        <v>0.2078802046455905</v>
+        <v>0.2078802046455763</v>
       </c>
       <c r="M99" s="131" t="n">
         <v>9.066045126289215</v>
       </c>
       <c r="N99" s="132" t="n">
-        <v>12.3359959176605</v>
+        <v>12.33599591766054</v>
       </c>
       <c r="P99" s="130" t="n">
-        <v>2.085521369386896</v>
+        <v>2.085521369386868</v>
       </c>
       <c r="Q99" s="131" t="n">
         <v>0.1405100237658985</v>
@@ -7238,10 +7238,10 @@
         <v>9.007694104937713</v>
       </c>
       <c r="T99" s="132" t="n">
-        <v>11.31506302751455</v>
+        <v>11.31506302751453</v>
       </c>
       <c r="V99" s="130" t="n">
-        <v>1.437311782396421</v>
+        <v>1.437311782396449</v>
       </c>
       <c r="W99" s="131" t="n">
         <v>0.1196840743637324</v>
@@ -7250,10 +7250,10 @@
         <v>0.07925896025579959</v>
       </c>
       <c r="Y99" s="131" t="n">
-        <v>8.986599287659089</v>
+        <v>8.986599287659086</v>
       </c>
       <c r="Z99" s="132" t="n">
-        <v>10.62285410467504</v>
+        <v>10.62285410467507</v>
       </c>
     </row>
     <row r="100">
@@ -7317,10 +7317,10 @@
         <v>0</v>
       </c>
       <c r="Y100" s="134" t="n">
-        <v>8.869397968855964</v>
+        <v>8.869397968855965</v>
       </c>
       <c r="Z100" s="135" t="n">
-        <v>8.869397968855964</v>
+        <v>8.869397968855965</v>
       </c>
     </row>
     <row r="101">
@@ -7513,7 +7513,7 @@
         <v>111.9494145335249</v>
       </c>
       <c r="V103" s="139" t="n">
-        <v>95.18610366019895</v>
+        <v>95.18610366019897</v>
       </c>
       <c r="W103" s="140" t="n">
         <v>51.83334773437532</v>
@@ -7550,7 +7550,7 @@
         <v>353</v>
       </c>
       <c r="J104" s="142" t="n">
-        <v>132.727068836402</v>
+        <v>132.7270688364021</v>
       </c>
       <c r="K104" s="143" t="n">
         <v>99.96010795959765</v>
@@ -7562,7 +7562,7 @@
         <v>33.18867931990665</v>
       </c>
       <c r="N104" s="144" t="n">
-        <v>398.9186558156983</v>
+        <v>398.9186558156985</v>
       </c>
       <c r="P104" s="142" t="n">
         <v>173.280619982703</v>
@@ -8702,7 +8702,7 @@
         </is>
       </c>
       <c r="AH26" s="122" t="n">
-        <v>26522.14923286874</v>
+        <v>26522.14923286875</v>
       </c>
       <c r="AI26" s="56" t="n">
         <v>63.51854929769291</v>
@@ -8936,7 +8936,7 @@
         <v>8558.030471186486</v>
       </c>
       <c r="AI29" s="56" t="n">
-        <v>6.942429228798463</v>
+        <v>6.942429228798462</v>
       </c>
       <c r="AK29" s="123" t="n">
         <v>5</v>
@@ -9144,7 +9144,7 @@
         </is>
       </c>
       <c r="AH32" s="122" t="n">
-        <v>5758.614189381809</v>
+        <v>5758.61418938181</v>
       </c>
       <c r="AI32" s="56" t="n">
         <v>9.141959392549317</v>
@@ -9672,7 +9672,7 @@
         <v>2718.813753475329</v>
       </c>
       <c r="AI39" s="56" t="n">
-        <v>6.787888704218473</v>
+        <v>6.787888704218474</v>
       </c>
       <c r="AK39" s="123" t="n">
         <v>15</v>
@@ -10429,10 +10429,10 @@
         <v>13</v>
       </c>
       <c r="J53" s="127" t="n">
-        <v>3.367208266425485</v>
+        <v>3.367208266425486</v>
       </c>
       <c r="K53" s="128" t="n">
-        <v>2.526596826732871</v>
+        <v>2.52659682673287</v>
       </c>
       <c r="L53" s="128" t="n">
         <v>5.050972602908543</v>
@@ -10450,7 +10450,7 @@
         <v>2.389684032962864</v>
       </c>
       <c r="R53" s="128" t="n">
-        <v>4.691096276623046</v>
+        <v>4.691096276623045</v>
       </c>
       <c r="S53" s="128" t="n">
         <v>0</v>
@@ -10471,7 +10471,7 @@
         <v>0</v>
       </c>
       <c r="Z53" s="129" t="n">
-        <v>9.726130306163938</v>
+        <v>9.726130306163936</v>
       </c>
       <c r="AE53" s="121" t="n">
         <v>5</v>
@@ -10563,7 +10563,7 @@
         </is>
       </c>
       <c r="AG54" s="122" t="n">
-        <v>5758.614189381809</v>
+        <v>5758.61418938181</v>
       </c>
       <c r="AH54" s="56" t="n">
         <v>9.141959392549317</v>
@@ -10591,7 +10591,7 @@
         <v>11</v>
       </c>
       <c r="J55" s="130" t="n">
-        <v>11.00421963992369</v>
+        <v>11.0042196399237</v>
       </c>
       <c r="K55" s="131" t="n">
         <v>0</v>
@@ -10603,7 +10603,7 @@
         <v>0</v>
       </c>
       <c r="N55" s="132" t="n">
-        <v>11.00421963992369</v>
+        <v>11.0042196399237</v>
       </c>
       <c r="P55" s="130" t="n">
         <v>11.25327823035992</v>
@@ -10621,7 +10621,7 @@
         <v>11.25327823035992</v>
       </c>
       <c r="V55" s="130" t="n">
-        <v>11.64231197178806</v>
+        <v>11.64231197178807</v>
       </c>
       <c r="W55" s="131" t="n">
         <v>0</v>
@@ -10633,7 +10633,7 @@
         <v>0</v>
       </c>
       <c r="Z55" s="132" t="n">
-        <v>11.64231197178806</v>
+        <v>11.64231197178807</v>
       </c>
       <c r="AE55" s="121" t="n">
         <v>7</v>
@@ -10756,10 +10756,10 @@
         <v>63.51701400863278</v>
       </c>
       <c r="K57" s="131" t="n">
-        <v>55.26075949714093</v>
+        <v>55.26075949714092</v>
       </c>
       <c r="L57" s="131" t="n">
-        <v>70.05762760070748</v>
+        <v>70.05762760070749</v>
       </c>
       <c r="M57" s="131" t="n">
         <v>0</v>
@@ -10768,13 +10768,13 @@
         <v>188.8354011064812</v>
       </c>
       <c r="P57" s="130" t="n">
-        <v>62.84620709537453</v>
+        <v>62.84620709537454</v>
       </c>
       <c r="Q57" s="131" t="n">
         <v>53.99726869828643</v>
       </c>
       <c r="R57" s="131" t="n">
-        <v>67.54614245337035</v>
+        <v>67.54614245337034</v>
       </c>
       <c r="S57" s="131" t="n">
         <v>0</v>
@@ -10789,7 +10789,7 @@
         <v>54.54301454127602</v>
       </c>
       <c r="X57" s="131" t="n">
-        <v>66.06395772949691</v>
+        <v>66.06395772949689</v>
       </c>
       <c r="Y57" s="131" t="n">
         <v>0</v>
@@ -11077,7 +11077,7 @@
         <v>72</v>
       </c>
       <c r="J61" s="130" t="n">
-        <v>33.80888039188297</v>
+        <v>33.80888039188298</v>
       </c>
       <c r="K61" s="131" t="n">
         <v>11.56721622874408</v>
@@ -11089,10 +11089,10 @@
         <v>0</v>
       </c>
       <c r="N61" s="132" t="n">
-        <v>72.42718278064054</v>
+        <v>72.42718278064055</v>
       </c>
       <c r="P61" s="130" t="n">
-        <v>34.38023379828336</v>
+        <v>34.38023379828337</v>
       </c>
       <c r="Q61" s="131" t="n">
         <v>11.88171813551708</v>
@@ -11113,7 +11113,7 @@
         <v>12.10617120330805</v>
       </c>
       <c r="X61" s="131" t="n">
-        <v>25.76138345852207</v>
+        <v>25.76138345852206</v>
       </c>
       <c r="Y61" s="131" t="n">
         <v>0</v>
@@ -11242,10 +11242,10 @@
         <v>2.58953491341282</v>
       </c>
       <c r="K63" s="131" t="n">
-        <v>0.4725356733129047</v>
+        <v>0.4725356733129189</v>
       </c>
       <c r="L63" s="131" t="n">
-        <v>0.2078802046455763</v>
+        <v>0.2078802046455621</v>
       </c>
       <c r="M63" s="131" t="n">
         <v>7.308333158315506</v>
@@ -11254,34 +11254,34 @@
         <v>10.57828394968681</v>
       </c>
       <c r="P63" s="130" t="n">
-        <v>2.085521369386882</v>
+        <v>2.085521369386896</v>
       </c>
       <c r="Q63" s="131" t="n">
-        <v>0.1405100237658843</v>
+        <v>0.1405100237658985</v>
       </c>
       <c r="R63" s="131" t="n">
-        <v>0.08133752942403305</v>
+        <v>0.08133752942404726</v>
       </c>
       <c r="S63" s="131" t="n">
         <v>6.991768917026942</v>
       </c>
       <c r="T63" s="132" t="n">
-        <v>9.299137839603741</v>
+        <v>9.299137839603784</v>
       </c>
       <c r="V63" s="130" t="n">
-        <v>1.437311782396435</v>
+        <v>1.437311782396449</v>
       </c>
       <c r="W63" s="131" t="n">
         <v>0.1196840743637324</v>
       </c>
       <c r="X63" s="131" t="n">
-        <v>0.07925896025578538</v>
+        <v>0.0792589602558138</v>
       </c>
       <c r="Y63" s="131" t="n">
-        <v>6.012182320226879</v>
+        <v>6.012182320226881</v>
       </c>
       <c r="Z63" s="132" t="n">
-        <v>7.648437137242832</v>
+        <v>7.648437137242876</v>
       </c>
       <c r="AE63" s="121" t="n">
         <v>15</v>
@@ -11344,10 +11344,10 @@
         <v>0</v>
       </c>
       <c r="S64" s="134" t="n">
-        <v>6.877622740410127</v>
+        <v>6.877622740410126</v>
       </c>
       <c r="T64" s="135" t="n">
-        <v>6.877622740410127</v>
+        <v>6.877622740410126</v>
       </c>
       <c r="V64" s="133" t="n">
         <v>0</v>
@@ -11359,10 +11359,10 @@
         <v>0</v>
       </c>
       <c r="Y64" s="134" t="n">
-        <v>5.894981001423755</v>
+        <v>5.894981001423756</v>
       </c>
       <c r="Z64" s="135" t="n">
-        <v>5.894981001423755</v>
+        <v>5.894981001423756</v>
       </c>
       <c r="AE64" s="121" t="n">
         <v>16</v>
@@ -11569,10 +11569,10 @@
         <v>0</v>
       </c>
       <c r="J67" s="139" t="n">
-        <v>2.893467696716072</v>
+        <v>2.893467696716073</v>
       </c>
       <c r="K67" s="140" t="n">
-        <v>3.224075867332796</v>
+        <v>3.224075867332795</v>
       </c>
       <c r="L67" s="140" t="n">
         <v>5.423006045073501</v>
@@ -11584,10 +11584,10 @@
         <v>14.94042145573816</v>
       </c>
       <c r="P67" s="139" t="n">
-        <v>5.575560697241529</v>
+        <v>5.575560697241528</v>
       </c>
       <c r="Q67" s="140" t="n">
-        <v>4.527875195047197</v>
+        <v>4.527875195047198</v>
       </c>
       <c r="R67" s="140" t="n">
         <v>5.836822602345891</v>
@@ -11599,7 +11599,7 @@
         <v>19.39887874626104</v>
       </c>
       <c r="V67" s="139" t="n">
-        <v>9.739762734353809</v>
+        <v>9.73976273435381</v>
       </c>
       <c r="W67" s="140" t="n">
         <v>5.762176317484299</v>
@@ -11692,7 +11692,7 @@
         <v>21.71266355619796</v>
       </c>
       <c r="Z68" s="144" t="n">
-        <v>326.3064173993097</v>
+        <v>326.3064173993098</v>
       </c>
       <c r="AE68" s="124" t="n">
         <v>20</v>
@@ -12881,7 +12881,7 @@
         <v>5.381189522398397</v>
       </c>
       <c r="N86" s="144" t="n">
-        <v>65.89275335765966</v>
+        <v>65.89275335765964</v>
       </c>
       <c r="P86" s="142" t="n">
         <v>53.95276536276727</v>
@@ -13065,10 +13065,10 @@
         <v>13</v>
       </c>
       <c r="J89" s="127" t="n">
-        <v>3.367208266425485</v>
+        <v>3.367208266425486</v>
       </c>
       <c r="K89" s="128" t="n">
-        <v>2.526596826732871</v>
+        <v>2.52659682673287</v>
       </c>
       <c r="L89" s="128" t="n">
         <v>5.050972602908543</v>
@@ -13086,7 +13086,7 @@
         <v>2.389684032962864</v>
       </c>
       <c r="R89" s="128" t="n">
-        <v>4.691096276623046</v>
+        <v>4.691096276623045</v>
       </c>
       <c r="S89" s="128" t="n">
         <v>0</v>
@@ -13107,7 +13107,7 @@
         <v>0</v>
       </c>
       <c r="Z89" s="129" t="n">
-        <v>9.726130306163938</v>
+        <v>9.726130306163936</v>
       </c>
     </row>
     <row r="90">
@@ -13199,7 +13199,7 @@
         <v>11</v>
       </c>
       <c r="J91" s="130" t="n">
-        <v>11.00421963992369</v>
+        <v>11.0042196399237</v>
       </c>
       <c r="K91" s="131" t="n">
         <v>0</v>
@@ -13211,7 +13211,7 @@
         <v>0</v>
       </c>
       <c r="N91" s="132" t="n">
-        <v>11.00421963992369</v>
+        <v>11.0042196399237</v>
       </c>
       <c r="P91" s="130" t="n">
         <v>11.25327823035992</v>
@@ -13229,7 +13229,7 @@
         <v>11.25327823035992</v>
       </c>
       <c r="V91" s="130" t="n">
-        <v>11.64231197178806</v>
+        <v>11.64231197178807</v>
       </c>
       <c r="W91" s="131" t="n">
         <v>0</v>
@@ -13241,7 +13241,7 @@
         <v>0</v>
       </c>
       <c r="Z91" s="132" t="n">
-        <v>11.64231197178806</v>
+        <v>11.64231197178807</v>
       </c>
     </row>
     <row r="92">
@@ -13336,10 +13336,10 @@
         <v>67.61543233395422</v>
       </c>
       <c r="K93" s="131" t="n">
-        <v>70.04432412598567</v>
+        <v>70.04432412598565</v>
       </c>
       <c r="L93" s="131" t="n">
-        <v>83.67502034869864</v>
+        <v>83.67502034869865</v>
       </c>
       <c r="M93" s="131" t="n">
         <v>0</v>
@@ -13348,13 +13348,13 @@
         <v>221.3347768086385</v>
       </c>
       <c r="P93" s="130" t="n">
-        <v>68.90194032977443</v>
+        <v>68.90194032977445</v>
       </c>
       <c r="Q93" s="131" t="n">
-        <v>72.96124159975149</v>
+        <v>72.96124159975147</v>
       </c>
       <c r="R93" s="131" t="n">
-        <v>83.61706243415738</v>
+        <v>83.61706243415736</v>
       </c>
       <c r="S93" s="131" t="n">
         <v>0</v>
@@ -13369,7 +13369,7 @@
         <v>75.74904598402861</v>
       </c>
       <c r="X93" s="131" t="n">
-        <v>84.21330605471455</v>
+        <v>84.21330605471454</v>
       </c>
       <c r="Y93" s="131" t="n">
         <v>0</v>
@@ -13601,7 +13601,7 @@
         <v>72</v>
       </c>
       <c r="J97" s="130" t="n">
-        <v>33.80888039188297</v>
+        <v>33.80888039188298</v>
       </c>
       <c r="K97" s="131" t="n">
         <v>11.56721622874408</v>
@@ -13613,10 +13613,10 @@
         <v>0</v>
       </c>
       <c r="N97" s="132" t="n">
-        <v>72.42718278064054</v>
+        <v>72.42718278064055</v>
       </c>
       <c r="P97" s="130" t="n">
-        <v>34.38023379828336</v>
+        <v>34.38023379828337</v>
       </c>
       <c r="Q97" s="131" t="n">
         <v>11.88171813551708</v>
@@ -13637,13 +13637,13 @@
         <v>12.10617120330805</v>
       </c>
       <c r="X97" s="131" t="n">
-        <v>28.98737431110368</v>
+        <v>28.98737431110367</v>
       </c>
       <c r="Y97" s="131" t="n">
         <v>0</v>
       </c>
       <c r="Z97" s="132" t="n">
-        <v>76.5085550051911</v>
+        <v>76.50855500519108</v>
       </c>
     </row>
     <row r="98">
@@ -13735,22 +13735,22 @@
         <v>9</v>
       </c>
       <c r="J99" s="130" t="n">
-        <v>2.589534913412791</v>
+        <v>2.58953491341282</v>
       </c>
       <c r="K99" s="131" t="n">
-        <v>0.4725356733129047</v>
+        <v>0.4725356733129331</v>
       </c>
       <c r="L99" s="131" t="n">
-        <v>0.2078802046455905</v>
+        <v>0.2078802046455763</v>
       </c>
       <c r="M99" s="131" t="n">
         <v>9.066045126289215</v>
       </c>
       <c r="N99" s="132" t="n">
-        <v>12.3359959176605</v>
+        <v>12.33599591766054</v>
       </c>
       <c r="P99" s="130" t="n">
-        <v>2.085521369386896</v>
+        <v>2.085521369386868</v>
       </c>
       <c r="Q99" s="131" t="n">
         <v>0.1405100237658985</v>
@@ -13762,10 +13762,10 @@
         <v>9.007694104937713</v>
       </c>
       <c r="T99" s="132" t="n">
-        <v>11.31506302751455</v>
+        <v>11.31506302751453</v>
       </c>
       <c r="V99" s="130" t="n">
-        <v>1.437311782396421</v>
+        <v>1.437311782396449</v>
       </c>
       <c r="W99" s="131" t="n">
         <v>0.1196840743637324</v>
@@ -13774,10 +13774,10 @@
         <v>0.07925896025579959</v>
       </c>
       <c r="Y99" s="131" t="n">
-        <v>8.986599287659089</v>
+        <v>8.986599287659086</v>
       </c>
       <c r="Z99" s="132" t="n">
-        <v>10.62285410467504</v>
+        <v>10.62285410467507</v>
       </c>
     </row>
     <row r="100">
@@ -13841,10 +13841,10 @@
         <v>0</v>
       </c>
       <c r="Y100" s="134" t="n">
-        <v>8.869397968855964</v>
+        <v>8.869397968855965</v>
       </c>
       <c r="Z100" s="135" t="n">
-        <v>8.869397968855964</v>
+        <v>8.869397968855965</v>
       </c>
     </row>
     <row r="101">
@@ -14037,7 +14037,7 @@
         <v>111.9494145335249</v>
       </c>
       <c r="V103" s="139" t="n">
-        <v>95.18610366019895</v>
+        <v>95.18610366019897</v>
       </c>
       <c r="W103" s="140" t="n">
         <v>51.83334773437532</v>
@@ -14074,7 +14074,7 @@
         <v>353</v>
       </c>
       <c r="J104" s="142" t="n">
-        <v>132.727068836402</v>
+        <v>132.7270688364021</v>
       </c>
       <c r="K104" s="143" t="n">
         <v>99.96010795959765</v>
@@ -14086,7 +14086,7 @@
         <v>33.18867931990665</v>
       </c>
       <c r="N104" s="144" t="n">
-        <v>398.9186558156983</v>
+        <v>398.9186558156985</v>
       </c>
       <c r="P104" s="142" t="n">
         <v>173.280619982703</v>
@@ -15380,10 +15380,10 @@
         </is>
       </c>
       <c r="AH28" s="122" t="n">
-        <v>9745.4290075194</v>
+        <v>9745.429007519399</v>
       </c>
       <c r="AI28" s="56" t="n">
-        <v>29.1474955513474</v>
+        <v>29.14749555134741</v>
       </c>
       <c r="AK28" s="123" t="n">
         <v>4</v>
@@ -15687,7 +15687,7 @@
         </is>
       </c>
       <c r="AN32" s="58" t="n">
-        <v>9.393915268543525</v>
+        <v>9.393915268543527</v>
       </c>
     </row>
     <row r="33">
@@ -16925,7 +16925,7 @@
         </is>
       </c>
       <c r="AG52" s="122" t="n">
-        <v>9745.4290075194</v>
+        <v>9745.429007519399</v>
       </c>
       <c r="AH52" s="56" t="n">
         <v>29.1474955513474</v>
@@ -16953,10 +16953,10 @@
         <v>13</v>
       </c>
       <c r="J53" s="127" t="n">
-        <v>3.367208266425485</v>
+        <v>3.367208266425486</v>
       </c>
       <c r="K53" s="128" t="n">
-        <v>2.526596826732871</v>
+        <v>2.52659682673287</v>
       </c>
       <c r="L53" s="128" t="n">
         <v>5.050972602908543</v>
@@ -16974,7 +16974,7 @@
         <v>2.389684032962864</v>
       </c>
       <c r="R53" s="128" t="n">
-        <v>4.691096276623046</v>
+        <v>4.691096276623045</v>
       </c>
       <c r="S53" s="128" t="n">
         <v>0</v>
@@ -16995,7 +16995,7 @@
         <v>0</v>
       </c>
       <c r="Z53" s="129" t="n">
-        <v>9.726130306163938</v>
+        <v>9.726130306163936</v>
       </c>
       <c r="AE53" s="121" t="n">
         <v>5</v>
@@ -17115,7 +17115,7 @@
         <v>11</v>
       </c>
       <c r="J55" s="130" t="n">
-        <v>11.00421963992369</v>
+        <v>11.0042196399237</v>
       </c>
       <c r="K55" s="131" t="n">
         <v>0</v>
@@ -17127,7 +17127,7 @@
         <v>0</v>
       </c>
       <c r="N55" s="132" t="n">
-        <v>11.00421963992369</v>
+        <v>11.0042196399237</v>
       </c>
       <c r="P55" s="130" t="n">
         <v>11.25327823035992</v>
@@ -17145,7 +17145,7 @@
         <v>11.25327823035992</v>
       </c>
       <c r="V55" s="130" t="n">
-        <v>11.64231197178806</v>
+        <v>11.64231197178807</v>
       </c>
       <c r="W55" s="131" t="n">
         <v>0</v>
@@ -17157,7 +17157,7 @@
         <v>0</v>
       </c>
       <c r="Z55" s="132" t="n">
-        <v>11.64231197178806</v>
+        <v>11.64231197178807</v>
       </c>
       <c r="AE55" s="121" t="n">
         <v>7</v>
@@ -17280,10 +17280,10 @@
         <v>63.51701400863278</v>
       </c>
       <c r="K57" s="131" t="n">
-        <v>55.26075949714093</v>
+        <v>55.26075949714092</v>
       </c>
       <c r="L57" s="131" t="n">
-        <v>70.05762760070748</v>
+        <v>70.05762760070749</v>
       </c>
       <c r="M57" s="131" t="n">
         <v>0</v>
@@ -17292,13 +17292,13 @@
         <v>188.8354011064812</v>
       </c>
       <c r="P57" s="130" t="n">
-        <v>62.84620709537453</v>
+        <v>62.84620709537454</v>
       </c>
       <c r="Q57" s="131" t="n">
         <v>53.99726869828643</v>
       </c>
       <c r="R57" s="131" t="n">
-        <v>67.54614245337035</v>
+        <v>67.54614245337034</v>
       </c>
       <c r="S57" s="131" t="n">
         <v>0</v>
@@ -17313,7 +17313,7 @@
         <v>54.54301454127602</v>
       </c>
       <c r="X57" s="131" t="n">
-        <v>66.06395772949691</v>
+        <v>66.06395772949689</v>
       </c>
       <c r="Y57" s="131" t="n">
         <v>0</v>
@@ -17601,7 +17601,7 @@
         <v>72</v>
       </c>
       <c r="J61" s="130" t="n">
-        <v>33.80888039188297</v>
+        <v>33.80888039188298</v>
       </c>
       <c r="K61" s="131" t="n">
         <v>11.56721622874408</v>
@@ -17613,10 +17613,10 @@
         <v>0</v>
       </c>
       <c r="N61" s="132" t="n">
-        <v>72.42718278064054</v>
+        <v>72.42718278064055</v>
       </c>
       <c r="P61" s="130" t="n">
-        <v>34.38023379828336</v>
+        <v>34.38023379828337</v>
       </c>
       <c r="Q61" s="131" t="n">
         <v>11.88171813551708</v>
@@ -17637,7 +17637,7 @@
         <v>12.10617120330805</v>
       </c>
       <c r="X61" s="131" t="n">
-        <v>25.76138345852207</v>
+        <v>25.76138345852206</v>
       </c>
       <c r="Y61" s="131" t="n">
         <v>0</v>
@@ -17766,10 +17766,10 @@
         <v>2.58953491341282</v>
       </c>
       <c r="K63" s="131" t="n">
-        <v>0.4725356733129047</v>
+        <v>0.4725356733129189</v>
       </c>
       <c r="L63" s="131" t="n">
-        <v>0.2078802046455763</v>
+        <v>0.2078802046455621</v>
       </c>
       <c r="M63" s="131" t="n">
         <v>7.308333158315506</v>
@@ -17778,34 +17778,34 @@
         <v>10.57828394968681</v>
       </c>
       <c r="P63" s="130" t="n">
-        <v>2.085521369386882</v>
+        <v>2.085521369386896</v>
       </c>
       <c r="Q63" s="131" t="n">
-        <v>0.1405100237658843</v>
+        <v>0.1405100237658985</v>
       </c>
       <c r="R63" s="131" t="n">
-        <v>0.08133752942403305</v>
+        <v>0.08133752942404726</v>
       </c>
       <c r="S63" s="131" t="n">
         <v>6.991768917026942</v>
       </c>
       <c r="T63" s="132" t="n">
-        <v>9.299137839603741</v>
+        <v>9.299137839603784</v>
       </c>
       <c r="V63" s="130" t="n">
-        <v>1.437311782396435</v>
+        <v>1.437311782396449</v>
       </c>
       <c r="W63" s="131" t="n">
         <v>0.1196840743637324</v>
       </c>
       <c r="X63" s="131" t="n">
-        <v>0.07925896025578538</v>
+        <v>0.0792589602558138</v>
       </c>
       <c r="Y63" s="131" t="n">
-        <v>6.012182320226879</v>
+        <v>6.012182320226881</v>
       </c>
       <c r="Z63" s="132" t="n">
-        <v>7.648437137242832</v>
+        <v>7.648437137242876</v>
       </c>
       <c r="AE63" s="121" t="n">
         <v>15</v>
@@ -17868,10 +17868,10 @@
         <v>0</v>
       </c>
       <c r="S64" s="134" t="n">
-        <v>6.877622740410127</v>
+        <v>6.877622740410126</v>
       </c>
       <c r="T64" s="135" t="n">
-        <v>6.877622740410127</v>
+        <v>6.877622740410126</v>
       </c>
       <c r="V64" s="133" t="n">
         <v>0</v>
@@ -17883,10 +17883,10 @@
         <v>0</v>
       </c>
       <c r="Y64" s="134" t="n">
-        <v>5.894981001423755</v>
+        <v>5.894981001423756</v>
       </c>
       <c r="Z64" s="135" t="n">
-        <v>5.894981001423755</v>
+        <v>5.894981001423756</v>
       </c>
       <c r="AE64" s="121" t="n">
         <v>16</v>
@@ -18093,10 +18093,10 @@
         <v>0</v>
       </c>
       <c r="J67" s="139" t="n">
-        <v>2.893467696716072</v>
+        <v>2.893467696716073</v>
       </c>
       <c r="K67" s="140" t="n">
-        <v>3.224075867332796</v>
+        <v>3.224075867332795</v>
       </c>
       <c r="L67" s="140" t="n">
         <v>5.423006045073501</v>
@@ -18108,10 +18108,10 @@
         <v>14.94042145573816</v>
       </c>
       <c r="P67" s="139" t="n">
-        <v>5.575560697241529</v>
+        <v>5.575560697241528</v>
       </c>
       <c r="Q67" s="140" t="n">
-        <v>4.527875195047197</v>
+        <v>4.527875195047198</v>
       </c>
       <c r="R67" s="140" t="n">
         <v>5.836822602345891</v>
@@ -18123,7 +18123,7 @@
         <v>19.39887874626104</v>
       </c>
       <c r="V67" s="139" t="n">
-        <v>9.739762734353809</v>
+        <v>9.73976273435381</v>
       </c>
       <c r="W67" s="140" t="n">
         <v>5.762176317484299</v>
@@ -18216,7 +18216,7 @@
         <v>21.71266355619796</v>
       </c>
       <c r="Z68" s="144" t="n">
-        <v>326.3064173993097</v>
+        <v>326.3064173993098</v>
       </c>
       <c r="AE68" s="124" t="n">
         <v>20</v>
@@ -19405,7 +19405,7 @@
         <v>5.381189522398397</v>
       </c>
       <c r="N86" s="144" t="n">
-        <v>65.89275335765966</v>
+        <v>65.89275335765964</v>
       </c>
       <c r="P86" s="142" t="n">
         <v>53.95276536276727</v>
@@ -19589,10 +19589,10 @@
         <v>13</v>
       </c>
       <c r="J89" s="127" t="n">
-        <v>3.367208266425485</v>
+        <v>3.367208266425486</v>
       </c>
       <c r="K89" s="128" t="n">
-        <v>2.526596826732871</v>
+        <v>2.52659682673287</v>
       </c>
       <c r="L89" s="128" t="n">
         <v>5.050972602908543</v>
@@ -19610,7 +19610,7 @@
         <v>2.389684032962864</v>
       </c>
       <c r="R89" s="128" t="n">
-        <v>4.691096276623046</v>
+        <v>4.691096276623045</v>
       </c>
       <c r="S89" s="128" t="n">
         <v>0</v>
@@ -19631,7 +19631,7 @@
         <v>0</v>
       </c>
       <c r="Z89" s="129" t="n">
-        <v>9.726130306163938</v>
+        <v>9.726130306163936</v>
       </c>
     </row>
     <row r="90">
@@ -19723,7 +19723,7 @@
         <v>11</v>
       </c>
       <c r="J91" s="130" t="n">
-        <v>11.00421963992369</v>
+        <v>11.0042196399237</v>
       </c>
       <c r="K91" s="131" t="n">
         <v>0</v>
@@ -19735,7 +19735,7 @@
         <v>0</v>
       </c>
       <c r="N91" s="132" t="n">
-        <v>11.00421963992369</v>
+        <v>11.0042196399237</v>
       </c>
       <c r="P91" s="130" t="n">
         <v>11.25327823035992</v>
@@ -19753,7 +19753,7 @@
         <v>11.25327823035992</v>
       </c>
       <c r="V91" s="130" t="n">
-        <v>11.64231197178806</v>
+        <v>11.64231197178807</v>
       </c>
       <c r="W91" s="131" t="n">
         <v>0</v>
@@ -19765,7 +19765,7 @@
         <v>0</v>
       </c>
       <c r="Z91" s="132" t="n">
-        <v>11.64231197178806</v>
+        <v>11.64231197178807</v>
       </c>
     </row>
     <row r="92">
@@ -19860,10 +19860,10 @@
         <v>67.61543233395422</v>
       </c>
       <c r="K93" s="131" t="n">
-        <v>70.04432412598567</v>
+        <v>70.04432412598565</v>
       </c>
       <c r="L93" s="131" t="n">
-        <v>83.67502034869864</v>
+        <v>83.67502034869865</v>
       </c>
       <c r="M93" s="131" t="n">
         <v>0</v>
@@ -19872,13 +19872,13 @@
         <v>221.3347768086385</v>
       </c>
       <c r="P93" s="130" t="n">
-        <v>68.90194032977443</v>
+        <v>68.90194032977445</v>
       </c>
       <c r="Q93" s="131" t="n">
-        <v>72.96124159975149</v>
+        <v>72.96124159975147</v>
       </c>
       <c r="R93" s="131" t="n">
-        <v>83.61706243415738</v>
+        <v>83.61706243415736</v>
       </c>
       <c r="S93" s="131" t="n">
         <v>0</v>
@@ -19893,7 +19893,7 @@
         <v>75.74904598402861</v>
       </c>
       <c r="X93" s="131" t="n">
-        <v>84.21330605471455</v>
+        <v>84.21330605471454</v>
       </c>
       <c r="Y93" s="131" t="n">
         <v>0</v>
@@ -20125,7 +20125,7 @@
         <v>72</v>
       </c>
       <c r="J97" s="130" t="n">
-        <v>33.80888039188297</v>
+        <v>33.80888039188298</v>
       </c>
       <c r="K97" s="131" t="n">
         <v>11.56721622874408</v>
@@ -20137,10 +20137,10 @@
         <v>0</v>
       </c>
       <c r="N97" s="132" t="n">
-        <v>72.42718278064054</v>
+        <v>72.42718278064055</v>
       </c>
       <c r="P97" s="130" t="n">
-        <v>34.38023379828336</v>
+        <v>34.38023379828337</v>
       </c>
       <c r="Q97" s="131" t="n">
         <v>11.88171813551708</v>
@@ -20161,13 +20161,13 @@
         <v>12.10617120330805</v>
       </c>
       <c r="X97" s="131" t="n">
-        <v>28.98737431110368</v>
+        <v>28.98737431110367</v>
       </c>
       <c r="Y97" s="131" t="n">
         <v>0</v>
       </c>
       <c r="Z97" s="132" t="n">
-        <v>76.5085550051911</v>
+        <v>76.50855500519108</v>
       </c>
     </row>
     <row r="98">
@@ -20259,22 +20259,22 @@
         <v>9</v>
       </c>
       <c r="J99" s="130" t="n">
-        <v>2.589534913412791</v>
+        <v>2.58953491341282</v>
       </c>
       <c r="K99" s="131" t="n">
-        <v>0.4725356733129047</v>
+        <v>0.4725356733129331</v>
       </c>
       <c r="L99" s="131" t="n">
-        <v>0.2078802046455905</v>
+        <v>0.2078802046455763</v>
       </c>
       <c r="M99" s="131" t="n">
         <v>9.066045126289215</v>
       </c>
       <c r="N99" s="132" t="n">
-        <v>12.3359959176605</v>
+        <v>12.33599591766054</v>
       </c>
       <c r="P99" s="130" t="n">
-        <v>2.085521369386896</v>
+        <v>2.085521369386868</v>
       </c>
       <c r="Q99" s="131" t="n">
         <v>0.1405100237658985</v>
@@ -20286,10 +20286,10 @@
         <v>9.007694104937713</v>
       </c>
       <c r="T99" s="132" t="n">
-        <v>11.31506302751455</v>
+        <v>11.31506302751453</v>
       </c>
       <c r="V99" s="130" t="n">
-        <v>1.437311782396421</v>
+        <v>1.437311782396449</v>
       </c>
       <c r="W99" s="131" t="n">
         <v>0.1196840743637324</v>
@@ -20298,10 +20298,10 @@
         <v>0.07925896025579959</v>
       </c>
       <c r="Y99" s="131" t="n">
-        <v>8.986599287659089</v>
+        <v>8.986599287659086</v>
       </c>
       <c r="Z99" s="132" t="n">
-        <v>10.62285410467504</v>
+        <v>10.62285410467507</v>
       </c>
     </row>
     <row r="100">
@@ -20365,10 +20365,10 @@
         <v>0</v>
       </c>
       <c r="Y100" s="134" t="n">
-        <v>8.869397968855964</v>
+        <v>8.869397968855965</v>
       </c>
       <c r="Z100" s="135" t="n">
-        <v>8.869397968855964</v>
+        <v>8.869397968855965</v>
       </c>
     </row>
     <row r="101">
@@ -20561,7 +20561,7 @@
         <v>111.9494145335249</v>
       </c>
       <c r="V103" s="139" t="n">
-        <v>95.18610366019895</v>
+        <v>95.18610366019897</v>
       </c>
       <c r="W103" s="140" t="n">
         <v>51.83334773437532</v>
@@ -20598,7 +20598,7 @@
         <v>353</v>
       </c>
       <c r="J104" s="142" t="n">
-        <v>132.727068836402</v>
+        <v>132.7270688364021</v>
       </c>
       <c r="K104" s="143" t="n">
         <v>99.96010795959765</v>
@@ -20610,7 +20610,7 @@
         <v>33.18867931990665</v>
       </c>
       <c r="N104" s="144" t="n">
-        <v>398.9186558156983</v>
+        <v>398.9186558156985</v>
       </c>
       <c r="P104" s="142" t="n">
         <v>173.280619982703</v>
@@ -22121,7 +22121,7 @@
         </is>
       </c>
       <c r="AH31" s="122" t="n">
-        <v>6254.517428753081</v>
+        <v>6254.51742875308</v>
       </c>
       <c r="AI31" s="56" t="n">
         <v>9.116896294001295</v>
@@ -23269,7 +23269,7 @@
         <v>87555.74838878366</v>
       </c>
       <c r="AH49" s="46" t="n">
-        <v>68.10200542396777</v>
+        <v>68.10200542396778</v>
       </c>
     </row>
     <row r="50" ht="15" customHeight="1" thickBot="1">
@@ -23477,10 +23477,10 @@
         <v>13</v>
       </c>
       <c r="J53" s="127" t="n">
-        <v>3.367208266425485</v>
+        <v>3.367208266425486</v>
       </c>
       <c r="K53" s="128" t="n">
-        <v>2.526596826732871</v>
+        <v>2.52659682673287</v>
       </c>
       <c r="L53" s="128" t="n">
         <v>5.050972602908543</v>
@@ -23498,7 +23498,7 @@
         <v>2.389684032962864</v>
       </c>
       <c r="R53" s="128" t="n">
-        <v>4.691096276623046</v>
+        <v>4.691096276623045</v>
       </c>
       <c r="S53" s="128" t="n">
         <v>0</v>
@@ -23519,7 +23519,7 @@
         <v>0</v>
       </c>
       <c r="Z53" s="129" t="n">
-        <v>9.726130306163938</v>
+        <v>9.726130306163936</v>
       </c>
       <c r="AE53" s="121" t="n">
         <v>5</v>
@@ -23639,7 +23639,7 @@
         <v>11</v>
       </c>
       <c r="J55" s="130" t="n">
-        <v>11.00421963992369</v>
+        <v>11.0042196399237</v>
       </c>
       <c r="K55" s="131" t="n">
         <v>0</v>
@@ -23651,7 +23651,7 @@
         <v>0</v>
       </c>
       <c r="N55" s="132" t="n">
-        <v>11.00421963992369</v>
+        <v>11.0042196399237</v>
       </c>
       <c r="P55" s="130" t="n">
         <v>11.25327823035992</v>
@@ -23669,7 +23669,7 @@
         <v>11.25327823035992</v>
       </c>
       <c r="V55" s="130" t="n">
-        <v>11.64231197178806</v>
+        <v>11.64231197178807</v>
       </c>
       <c r="W55" s="131" t="n">
         <v>0</v>
@@ -23681,7 +23681,7 @@
         <v>0</v>
       </c>
       <c r="Z55" s="132" t="n">
-        <v>11.64231197178806</v>
+        <v>11.64231197178807</v>
       </c>
       <c r="AE55" s="121" t="n">
         <v>7</v>
@@ -23804,10 +23804,10 @@
         <v>63.51701400863278</v>
       </c>
       <c r="K57" s="131" t="n">
-        <v>55.26075949714093</v>
+        <v>55.26075949714092</v>
       </c>
       <c r="L57" s="131" t="n">
-        <v>70.05762760070748</v>
+        <v>70.05762760070749</v>
       </c>
       <c r="M57" s="131" t="n">
         <v>0</v>
@@ -23816,13 +23816,13 @@
         <v>188.8354011064812</v>
       </c>
       <c r="P57" s="130" t="n">
-        <v>62.84620709537453</v>
+        <v>62.84620709537454</v>
       </c>
       <c r="Q57" s="131" t="n">
         <v>53.99726869828643</v>
       </c>
       <c r="R57" s="131" t="n">
-        <v>67.54614245337035</v>
+        <v>67.54614245337034</v>
       </c>
       <c r="S57" s="131" t="n">
         <v>0</v>
@@ -23837,7 +23837,7 @@
         <v>54.54301454127602</v>
       </c>
       <c r="X57" s="131" t="n">
-        <v>66.06395772949691</v>
+        <v>66.06395772949689</v>
       </c>
       <c r="Y57" s="131" t="n">
         <v>0</v>
@@ -24125,7 +24125,7 @@
         <v>72</v>
       </c>
       <c r="J61" s="130" t="n">
-        <v>33.80888039188297</v>
+        <v>33.80888039188298</v>
       </c>
       <c r="K61" s="131" t="n">
         <v>11.56721622874408</v>
@@ -24137,10 +24137,10 @@
         <v>0</v>
       </c>
       <c r="N61" s="132" t="n">
-        <v>72.42718278064054</v>
+        <v>72.42718278064055</v>
       </c>
       <c r="P61" s="130" t="n">
-        <v>34.38023379828336</v>
+        <v>34.38023379828337</v>
       </c>
       <c r="Q61" s="131" t="n">
         <v>11.88171813551708</v>
@@ -24161,7 +24161,7 @@
         <v>12.10617120330805</v>
       </c>
       <c r="X61" s="131" t="n">
-        <v>25.76138345852207</v>
+        <v>25.76138345852206</v>
       </c>
       <c r="Y61" s="131" t="n">
         <v>0</v>
@@ -24290,10 +24290,10 @@
         <v>2.58953491341282</v>
       </c>
       <c r="K63" s="131" t="n">
-        <v>0.4725356733129047</v>
+        <v>0.4725356733129189</v>
       </c>
       <c r="L63" s="131" t="n">
-        <v>0.2078802046455763</v>
+        <v>0.2078802046455621</v>
       </c>
       <c r="M63" s="131" t="n">
         <v>7.308333158315506</v>
@@ -24302,34 +24302,34 @@
         <v>10.57828394968681</v>
       </c>
       <c r="P63" s="130" t="n">
-        <v>2.085521369386882</v>
+        <v>2.085521369386896</v>
       </c>
       <c r="Q63" s="131" t="n">
-        <v>0.1405100237658843</v>
+        <v>0.1405100237658985</v>
       </c>
       <c r="R63" s="131" t="n">
-        <v>0.08133752942403305</v>
+        <v>0.08133752942404726</v>
       </c>
       <c r="S63" s="131" t="n">
         <v>6.991768917026942</v>
       </c>
       <c r="T63" s="132" t="n">
-        <v>9.299137839603741</v>
+        <v>9.299137839603784</v>
       </c>
       <c r="V63" s="130" t="n">
-        <v>1.437311782396435</v>
+        <v>1.437311782396449</v>
       </c>
       <c r="W63" s="131" t="n">
         <v>0.1196840743637324</v>
       </c>
       <c r="X63" s="131" t="n">
-        <v>0.07925896025578538</v>
+        <v>0.0792589602558138</v>
       </c>
       <c r="Y63" s="131" t="n">
-        <v>6.012182320226879</v>
+        <v>6.012182320226881</v>
       </c>
       <c r="Z63" s="132" t="n">
-        <v>7.648437137242832</v>
+        <v>7.648437137242876</v>
       </c>
       <c r="AE63" s="121" t="n">
         <v>15</v>
@@ -24392,10 +24392,10 @@
         <v>0</v>
       </c>
       <c r="S64" s="134" t="n">
-        <v>6.877622740410127</v>
+        <v>6.877622740410126</v>
       </c>
       <c r="T64" s="135" t="n">
-        <v>6.877622740410127</v>
+        <v>6.877622740410126</v>
       </c>
       <c r="V64" s="133" t="n">
         <v>0</v>
@@ -24407,10 +24407,10 @@
         <v>0</v>
       </c>
       <c r="Y64" s="134" t="n">
-        <v>5.894981001423755</v>
+        <v>5.894981001423756</v>
       </c>
       <c r="Z64" s="135" t="n">
-        <v>5.894981001423755</v>
+        <v>5.894981001423756</v>
       </c>
       <c r="AE64" s="121" t="n">
         <v>16</v>
@@ -24617,10 +24617,10 @@
         <v>0</v>
       </c>
       <c r="J67" s="139" t="n">
-        <v>2.893467696716072</v>
+        <v>2.893467696716073</v>
       </c>
       <c r="K67" s="140" t="n">
-        <v>3.224075867332796</v>
+        <v>3.224075867332795</v>
       </c>
       <c r="L67" s="140" t="n">
         <v>5.423006045073501</v>
@@ -24632,10 +24632,10 @@
         <v>14.94042145573816</v>
       </c>
       <c r="P67" s="139" t="n">
-        <v>5.575560697241529</v>
+        <v>5.575560697241528</v>
       </c>
       <c r="Q67" s="140" t="n">
-        <v>4.527875195047197</v>
+        <v>4.527875195047198</v>
       </c>
       <c r="R67" s="140" t="n">
         <v>5.836822602345891</v>
@@ -24647,7 +24647,7 @@
         <v>19.39887874626104</v>
       </c>
       <c r="V67" s="139" t="n">
-        <v>9.739762734353809</v>
+        <v>9.73976273435381</v>
       </c>
       <c r="W67" s="140" t="n">
         <v>5.762176317484299</v>
@@ -24731,7 +24731,7 @@
         <v>21.71266355619796</v>
       </c>
       <c r="Z68" s="144" t="n">
-        <v>326.3064173993097</v>
+        <v>326.3064173993098</v>
       </c>
       <c r="AE68" s="124" t="n">
         <v>20</v>
@@ -25912,7 +25912,7 @@
         <v>5.381189522398397</v>
       </c>
       <c r="N86" s="144" t="n">
-        <v>65.89275335765966</v>
+        <v>65.89275335765964</v>
       </c>
       <c r="P86" s="142" t="n">
         <v>53.95276536276727</v>
@@ -26096,10 +26096,10 @@
         <v>13</v>
       </c>
       <c r="J89" s="127" t="n">
-        <v>3.367208266425485</v>
+        <v>3.367208266425486</v>
       </c>
       <c r="K89" s="128" t="n">
-        <v>2.526596826732871</v>
+        <v>2.52659682673287</v>
       </c>
       <c r="L89" s="128" t="n">
         <v>5.050972602908543</v>
@@ -26117,7 +26117,7 @@
         <v>2.389684032962864</v>
       </c>
       <c r="R89" s="128" t="n">
-        <v>4.691096276623046</v>
+        <v>4.691096276623045</v>
       </c>
       <c r="S89" s="128" t="n">
         <v>0</v>
@@ -26138,7 +26138,7 @@
         <v>0</v>
       </c>
       <c r="Z89" s="129" t="n">
-        <v>9.726130306163938</v>
+        <v>9.726130306163936</v>
       </c>
     </row>
     <row r="90">
@@ -26230,7 +26230,7 @@
         <v>11</v>
       </c>
       <c r="J91" s="130" t="n">
-        <v>11.00421963992369</v>
+        <v>11.0042196399237</v>
       </c>
       <c r="K91" s="131" t="n">
         <v>0</v>
@@ -26242,7 +26242,7 @@
         <v>0</v>
       </c>
       <c r="N91" s="132" t="n">
-        <v>11.00421963992369</v>
+        <v>11.0042196399237</v>
       </c>
       <c r="P91" s="130" t="n">
         <v>11.25327823035992</v>
@@ -26260,7 +26260,7 @@
         <v>11.25327823035992</v>
       </c>
       <c r="V91" s="130" t="n">
-        <v>11.64231197178806</v>
+        <v>11.64231197178807</v>
       </c>
       <c r="W91" s="131" t="n">
         <v>0</v>
@@ -26272,7 +26272,7 @@
         <v>0</v>
       </c>
       <c r="Z91" s="132" t="n">
-        <v>11.64231197178806</v>
+        <v>11.64231197178807</v>
       </c>
     </row>
     <row r="92">
@@ -26367,10 +26367,10 @@
         <v>67.61543233395422</v>
       </c>
       <c r="K93" s="131" t="n">
-        <v>70.04432412598567</v>
+        <v>70.04432412598565</v>
       </c>
       <c r="L93" s="131" t="n">
-        <v>83.67502034869864</v>
+        <v>83.67502034869865</v>
       </c>
       <c r="M93" s="131" t="n">
         <v>0</v>
@@ -26379,13 +26379,13 @@
         <v>221.3347768086385</v>
       </c>
       <c r="P93" s="130" t="n">
-        <v>68.90194032977443</v>
+        <v>68.90194032977445</v>
       </c>
       <c r="Q93" s="131" t="n">
-        <v>72.96124159975149</v>
+        <v>72.96124159975147</v>
       </c>
       <c r="R93" s="131" t="n">
-        <v>83.61706243415738</v>
+        <v>83.61706243415736</v>
       </c>
       <c r="S93" s="131" t="n">
         <v>0</v>
@@ -26400,7 +26400,7 @@
         <v>75.74904598402861</v>
       </c>
       <c r="X93" s="131" t="n">
-        <v>84.21330605471455</v>
+        <v>84.21330605471454</v>
       </c>
       <c r="Y93" s="131" t="n">
         <v>0</v>
@@ -26632,7 +26632,7 @@
         <v>72</v>
       </c>
       <c r="J97" s="130" t="n">
-        <v>33.80888039188297</v>
+        <v>33.80888039188298</v>
       </c>
       <c r="K97" s="131" t="n">
         <v>11.56721622874408</v>
@@ -26644,10 +26644,10 @@
         <v>0</v>
       </c>
       <c r="N97" s="132" t="n">
-        <v>72.42718278064054</v>
+        <v>72.42718278064055</v>
       </c>
       <c r="P97" s="130" t="n">
-        <v>34.38023379828336</v>
+        <v>34.38023379828337</v>
       </c>
       <c r="Q97" s="131" t="n">
         <v>11.88171813551708</v>
@@ -26668,13 +26668,13 @@
         <v>12.10617120330805</v>
       </c>
       <c r="X97" s="131" t="n">
-        <v>28.98737431110368</v>
+        <v>28.98737431110367</v>
       </c>
       <c r="Y97" s="131" t="n">
         <v>0</v>
       </c>
       <c r="Z97" s="132" t="n">
-        <v>76.5085550051911</v>
+        <v>76.50855500519108</v>
       </c>
     </row>
     <row r="98">
@@ -26766,22 +26766,22 @@
         <v>9</v>
       </c>
       <c r="J99" s="130" t="n">
-        <v>2.589534913412791</v>
+        <v>2.58953491341282</v>
       </c>
       <c r="K99" s="131" t="n">
-        <v>0.4725356733129047</v>
+        <v>0.4725356733129331</v>
       </c>
       <c r="L99" s="131" t="n">
-        <v>0.2078802046455905</v>
+        <v>0.2078802046455763</v>
       </c>
       <c r="M99" s="131" t="n">
         <v>9.066045126289215</v>
       </c>
       <c r="N99" s="132" t="n">
-        <v>12.3359959176605</v>
+        <v>12.33599591766054</v>
       </c>
       <c r="P99" s="130" t="n">
-        <v>2.085521369386896</v>
+        <v>2.085521369386868</v>
       </c>
       <c r="Q99" s="131" t="n">
         <v>0.1405100237658985</v>
@@ -26793,10 +26793,10 @@
         <v>9.007694104937713</v>
       </c>
       <c r="T99" s="132" t="n">
-        <v>11.31506302751455</v>
+        <v>11.31506302751453</v>
       </c>
       <c r="V99" s="130" t="n">
-        <v>1.437311782396421</v>
+        <v>1.437311782396449</v>
       </c>
       <c r="W99" s="131" t="n">
         <v>0.1196840743637324</v>
@@ -26805,10 +26805,10 @@
         <v>0.07925896025579959</v>
       </c>
       <c r="Y99" s="131" t="n">
-        <v>8.986599287659089</v>
+        <v>8.986599287659086</v>
       </c>
       <c r="Z99" s="132" t="n">
-        <v>10.62285410467504</v>
+        <v>10.62285410467507</v>
       </c>
     </row>
     <row r="100">
@@ -26872,10 +26872,10 @@
         <v>0</v>
       </c>
       <c r="Y100" s="134" t="n">
-        <v>8.869397968855964</v>
+        <v>8.869397968855965</v>
       </c>
       <c r="Z100" s="135" t="n">
-        <v>8.869397968855964</v>
+        <v>8.869397968855965</v>
       </c>
     </row>
     <row r="101">
@@ -27068,7 +27068,7 @@
         <v>111.9494145335249</v>
       </c>
       <c r="V103" s="139" t="n">
-        <v>95.18610366019895</v>
+        <v>95.18610366019897</v>
       </c>
       <c r="W103" s="140" t="n">
         <v>51.83334773437532</v>
@@ -27105,7 +27105,7 @@
         <v>353</v>
       </c>
       <c r="J104" s="142" t="n">
-        <v>132.727068836402</v>
+        <v>132.7270688364021</v>
       </c>
       <c r="K104" s="143" t="n">
         <v>99.96010795959765</v>
@@ -27117,7 +27117,7 @@
         <v>33.18867931990665</v>
       </c>
       <c r="N104" s="144" t="n">
-        <v>398.9186558156983</v>
+        <v>398.9186558156985</v>
       </c>
       <c r="P104" s="142" t="n">
         <v>173.280619982703</v>
@@ -28257,10 +28257,10 @@
         </is>
       </c>
       <c r="AH26" s="122" t="n">
-        <v>12751.78709975114</v>
+        <v>12751.78709975115</v>
       </c>
       <c r="AI26" s="56" t="n">
-        <v>36.68742939755558</v>
+        <v>36.68742939755559</v>
       </c>
       <c r="AK26" s="123" t="n">
         <v>2</v>
@@ -29984,10 +29984,10 @@
         <v>13</v>
       </c>
       <c r="J53" s="127" t="n">
-        <v>3.367208266425485</v>
+        <v>3.367208266425486</v>
       </c>
       <c r="K53" s="128" t="n">
-        <v>2.526596826732871</v>
+        <v>2.52659682673287</v>
       </c>
       <c r="L53" s="128" t="n">
         <v>5.050972602908543</v>
@@ -30005,7 +30005,7 @@
         <v>2.389684032962864</v>
       </c>
       <c r="R53" s="128" t="n">
-        <v>4.691096276623046</v>
+        <v>4.691096276623045</v>
       </c>
       <c r="S53" s="128" t="n">
         <v>0</v>
@@ -30026,7 +30026,7 @@
         <v>0</v>
       </c>
       <c r="Z53" s="129" t="n">
-        <v>9.726130306163938</v>
+        <v>9.726130306163936</v>
       </c>
       <c r="AE53" s="121" t="n">
         <v>5</v>
@@ -30146,7 +30146,7 @@
         <v>11</v>
       </c>
       <c r="J55" s="130" t="n">
-        <v>11.00421963992369</v>
+        <v>11.0042196399237</v>
       </c>
       <c r="K55" s="131" t="n">
         <v>0</v>
@@ -30158,7 +30158,7 @@
         <v>0</v>
       </c>
       <c r="N55" s="132" t="n">
-        <v>11.00421963992369</v>
+        <v>11.0042196399237</v>
       </c>
       <c r="P55" s="130" t="n">
         <v>11.25327823035992</v>
@@ -30176,7 +30176,7 @@
         <v>11.25327823035992</v>
       </c>
       <c r="V55" s="130" t="n">
-        <v>11.64231197178806</v>
+        <v>11.64231197178807</v>
       </c>
       <c r="W55" s="131" t="n">
         <v>0</v>
@@ -30188,7 +30188,7 @@
         <v>0</v>
       </c>
       <c r="Z55" s="132" t="n">
-        <v>11.64231197178806</v>
+        <v>11.64231197178807</v>
       </c>
       <c r="AE55" s="121" t="n">
         <v>7</v>
@@ -30311,10 +30311,10 @@
         <v>63.51701400863278</v>
       </c>
       <c r="K57" s="131" t="n">
-        <v>55.26075949714093</v>
+        <v>55.26075949714092</v>
       </c>
       <c r="L57" s="131" t="n">
-        <v>70.05762760070748</v>
+        <v>70.05762760070749</v>
       </c>
       <c r="M57" s="131" t="n">
         <v>0</v>
@@ -30323,13 +30323,13 @@
         <v>188.8354011064812</v>
       </c>
       <c r="P57" s="130" t="n">
-        <v>62.84620709537453</v>
+        <v>62.84620709537454</v>
       </c>
       <c r="Q57" s="131" t="n">
         <v>53.99726869828643</v>
       </c>
       <c r="R57" s="131" t="n">
-        <v>67.54614245337035</v>
+        <v>67.54614245337034</v>
       </c>
       <c r="S57" s="131" t="n">
         <v>0</v>
@@ -30344,7 +30344,7 @@
         <v>54.54301454127602</v>
       </c>
       <c r="X57" s="131" t="n">
-        <v>66.06395772949691</v>
+        <v>66.06395772949689</v>
       </c>
       <c r="Y57" s="131" t="n">
         <v>0</v>
@@ -30632,7 +30632,7 @@
         <v>72</v>
       </c>
       <c r="J61" s="130" t="n">
-        <v>33.80888039188297</v>
+        <v>33.80888039188298</v>
       </c>
       <c r="K61" s="131" t="n">
         <v>11.56721622874408</v>
@@ -30644,10 +30644,10 @@
         <v>0</v>
       </c>
       <c r="N61" s="132" t="n">
-        <v>72.42718278064054</v>
+        <v>72.42718278064055</v>
       </c>
       <c r="P61" s="130" t="n">
-        <v>34.38023379828336</v>
+        <v>34.38023379828337</v>
       </c>
       <c r="Q61" s="131" t="n">
         <v>11.88171813551708</v>
@@ -30668,7 +30668,7 @@
         <v>12.10617120330805</v>
       </c>
       <c r="X61" s="131" t="n">
-        <v>25.76138345852207</v>
+        <v>25.76138345852206</v>
       </c>
       <c r="Y61" s="131" t="n">
         <v>0</v>
@@ -30797,10 +30797,10 @@
         <v>2.58953491341282</v>
       </c>
       <c r="K63" s="131" t="n">
-        <v>0.4725356733129047</v>
+        <v>0.4725356733129189</v>
       </c>
       <c r="L63" s="131" t="n">
-        <v>0.2078802046455763</v>
+        <v>0.2078802046455621</v>
       </c>
       <c r="M63" s="131" t="n">
         <v>7.308333158315506</v>
@@ -30809,34 +30809,34 @@
         <v>10.57828394968681</v>
       </c>
       <c r="P63" s="130" t="n">
-        <v>2.085521369386882</v>
+        <v>2.085521369386896</v>
       </c>
       <c r="Q63" s="131" t="n">
-        <v>0.1405100237658843</v>
+        <v>0.1405100237658985</v>
       </c>
       <c r="R63" s="131" t="n">
-        <v>0.08133752942403305</v>
+        <v>0.08133752942404726</v>
       </c>
       <c r="S63" s="131" t="n">
         <v>6.991768917026942</v>
       </c>
       <c r="T63" s="132" t="n">
-        <v>9.299137839603741</v>
+        <v>9.299137839603784</v>
       </c>
       <c r="V63" s="130" t="n">
-        <v>1.437311782396435</v>
+        <v>1.437311782396449</v>
       </c>
       <c r="W63" s="131" t="n">
         <v>0.1196840743637324</v>
       </c>
       <c r="X63" s="131" t="n">
-        <v>0.07925896025578538</v>
+        <v>0.0792589602558138</v>
       </c>
       <c r="Y63" s="131" t="n">
-        <v>6.012182320226879</v>
+        <v>6.012182320226881</v>
       </c>
       <c r="Z63" s="132" t="n">
-        <v>7.648437137242832</v>
+        <v>7.648437137242876</v>
       </c>
       <c r="AE63" s="121" t="n">
         <v>15</v>
@@ -30899,10 +30899,10 @@
         <v>0</v>
       </c>
       <c r="S64" s="134" t="n">
-        <v>6.877622740410127</v>
+        <v>6.877622740410126</v>
       </c>
       <c r="T64" s="135" t="n">
-        <v>6.877622740410127</v>
+        <v>6.877622740410126</v>
       </c>
       <c r="V64" s="133" t="n">
         <v>0</v>
@@ -30914,10 +30914,10 @@
         <v>0</v>
       </c>
       <c r="Y64" s="134" t="n">
-        <v>5.894981001423755</v>
+        <v>5.894981001423756</v>
       </c>
       <c r="Z64" s="135" t="n">
-        <v>5.894981001423755</v>
+        <v>5.894981001423756</v>
       </c>
       <c r="AE64" s="121" t="n">
         <v>16</v>
@@ -31106,10 +31106,10 @@
         <v>0</v>
       </c>
       <c r="J67" s="139" t="n">
-        <v>2.893467696716072</v>
+        <v>2.893467696716073</v>
       </c>
       <c r="K67" s="140" t="n">
-        <v>3.224075867332796</v>
+        <v>3.224075867332795</v>
       </c>
       <c r="L67" s="140" t="n">
         <v>5.423006045073501</v>
@@ -31121,10 +31121,10 @@
         <v>14.94042145573816</v>
       </c>
       <c r="P67" s="139" t="n">
-        <v>5.575560697241529</v>
+        <v>5.575560697241528</v>
       </c>
       <c r="Q67" s="140" t="n">
-        <v>4.527875195047197</v>
+        <v>4.527875195047198</v>
       </c>
       <c r="R67" s="140" t="n">
         <v>5.836822602345891</v>
@@ -31136,7 +31136,7 @@
         <v>19.39887874626104</v>
       </c>
       <c r="V67" s="139" t="n">
-        <v>9.739762734353809</v>
+        <v>9.73976273435381</v>
       </c>
       <c r="W67" s="140" t="n">
         <v>5.762176317484299</v>
@@ -31220,7 +31220,7 @@
         <v>21.71266355619796</v>
       </c>
       <c r="Z68" s="144" t="n">
-        <v>326.3064173993097</v>
+        <v>326.3064173993098</v>
       </c>
       <c r="AE68" s="124" t="n">
         <v>20</v>
@@ -32401,7 +32401,7 @@
         <v>5.381189522398397</v>
       </c>
       <c r="N86" s="144" t="n">
-        <v>65.89275335765966</v>
+        <v>65.89275335765964</v>
       </c>
       <c r="P86" s="142" t="n">
         <v>53.95276536276727</v>
@@ -32585,10 +32585,10 @@
         <v>13</v>
       </c>
       <c r="J89" s="127" t="n">
-        <v>3.367208266425485</v>
+        <v>3.367208266425486</v>
       </c>
       <c r="K89" s="128" t="n">
-        <v>2.526596826732871</v>
+        <v>2.52659682673287</v>
       </c>
       <c r="L89" s="128" t="n">
         <v>5.050972602908543</v>
@@ -32606,7 +32606,7 @@
         <v>2.389684032962864</v>
       </c>
       <c r="R89" s="128" t="n">
-        <v>4.691096276623046</v>
+        <v>4.691096276623045</v>
       </c>
       <c r="S89" s="128" t="n">
         <v>0</v>
@@ -32627,7 +32627,7 @@
         <v>0</v>
       </c>
       <c r="Z89" s="129" t="n">
-        <v>9.726130306163938</v>
+        <v>9.726130306163936</v>
       </c>
     </row>
     <row r="90">
@@ -32719,7 +32719,7 @@
         <v>11</v>
       </c>
       <c r="J91" s="130" t="n">
-        <v>11.00421963992369</v>
+        <v>11.0042196399237</v>
       </c>
       <c r="K91" s="131" t="n">
         <v>0</v>
@@ -32731,7 +32731,7 @@
         <v>0</v>
       </c>
       <c r="N91" s="132" t="n">
-        <v>11.00421963992369</v>
+        <v>11.0042196399237</v>
       </c>
       <c r="P91" s="130" t="n">
         <v>11.25327823035992</v>
@@ -32749,7 +32749,7 @@
         <v>11.25327823035992</v>
       </c>
       <c r="V91" s="130" t="n">
-        <v>11.64231197178806</v>
+        <v>11.64231197178807</v>
       </c>
       <c r="W91" s="131" t="n">
         <v>0</v>
@@ -32761,7 +32761,7 @@
         <v>0</v>
       </c>
       <c r="Z91" s="132" t="n">
-        <v>11.64231197178806</v>
+        <v>11.64231197178807</v>
       </c>
     </row>
     <row r="92">
@@ -32856,10 +32856,10 @@
         <v>67.61543233395422</v>
       </c>
       <c r="K93" s="131" t="n">
-        <v>70.04432412598567</v>
+        <v>70.04432412598565</v>
       </c>
       <c r="L93" s="131" t="n">
-        <v>83.67502034869864</v>
+        <v>83.67502034869865</v>
       </c>
       <c r="M93" s="131" t="n">
         <v>0</v>
@@ -32868,13 +32868,13 @@
         <v>221.3347768086385</v>
       </c>
       <c r="P93" s="130" t="n">
-        <v>68.90194032977443</v>
+        <v>68.90194032977445</v>
       </c>
       <c r="Q93" s="131" t="n">
-        <v>72.96124159975149</v>
+        <v>72.96124159975147</v>
       </c>
       <c r="R93" s="131" t="n">
-        <v>83.61706243415738</v>
+        <v>83.61706243415736</v>
       </c>
       <c r="S93" s="131" t="n">
         <v>0</v>
@@ -32889,7 +32889,7 @@
         <v>75.74904598402861</v>
       </c>
       <c r="X93" s="131" t="n">
-        <v>84.21330605471455</v>
+        <v>84.21330605471454</v>
       </c>
       <c r="Y93" s="131" t="n">
         <v>0</v>
@@ -33121,7 +33121,7 @@
         <v>72</v>
       </c>
       <c r="J97" s="130" t="n">
-        <v>33.80888039188297</v>
+        <v>33.80888039188298</v>
       </c>
       <c r="K97" s="131" t="n">
         <v>11.56721622874408</v>
@@ -33133,10 +33133,10 @@
         <v>0</v>
       </c>
       <c r="N97" s="132" t="n">
-        <v>72.42718278064054</v>
+        <v>72.42718278064055</v>
       </c>
       <c r="P97" s="130" t="n">
-        <v>34.38023379828336</v>
+        <v>34.38023379828337</v>
       </c>
       <c r="Q97" s="131" t="n">
         <v>11.88171813551708</v>
@@ -33157,13 +33157,13 @@
         <v>12.10617120330805</v>
       </c>
       <c r="X97" s="131" t="n">
-        <v>28.98737431110368</v>
+        <v>28.98737431110367</v>
       </c>
       <c r="Y97" s="131" t="n">
         <v>0</v>
       </c>
       <c r="Z97" s="132" t="n">
-        <v>76.5085550051911</v>
+        <v>76.50855500519108</v>
       </c>
     </row>
     <row r="98">
@@ -33255,22 +33255,22 @@
         <v>9</v>
       </c>
       <c r="J99" s="130" t="n">
-        <v>2.589534913412791</v>
+        <v>2.58953491341282</v>
       </c>
       <c r="K99" s="131" t="n">
-        <v>0.4725356733129047</v>
+        <v>0.4725356733129331</v>
       </c>
       <c r="L99" s="131" t="n">
-        <v>0.2078802046455905</v>
+        <v>0.2078802046455763</v>
       </c>
       <c r="M99" s="131" t="n">
         <v>9.066045126289215</v>
       </c>
       <c r="N99" s="132" t="n">
-        <v>12.3359959176605</v>
+        <v>12.33599591766054</v>
       </c>
       <c r="P99" s="130" t="n">
-        <v>2.085521369386896</v>
+        <v>2.085521369386868</v>
       </c>
       <c r="Q99" s="131" t="n">
         <v>0.1405100237658985</v>
@@ -33282,10 +33282,10 @@
         <v>9.007694104937713</v>
       </c>
       <c r="T99" s="132" t="n">
-        <v>11.31506302751455</v>
+        <v>11.31506302751453</v>
       </c>
       <c r="V99" s="130" t="n">
-        <v>1.437311782396421</v>
+        <v>1.437311782396449</v>
       </c>
       <c r="W99" s="131" t="n">
         <v>0.1196840743637324</v>
@@ -33294,10 +33294,10 @@
         <v>0.07925896025579959</v>
       </c>
       <c r="Y99" s="131" t="n">
-        <v>8.986599287659089</v>
+        <v>8.986599287659086</v>
       </c>
       <c r="Z99" s="132" t="n">
-        <v>10.62285410467504</v>
+        <v>10.62285410467507</v>
       </c>
     </row>
     <row r="100">
@@ -33361,10 +33361,10 @@
         <v>0</v>
       </c>
       <c r="Y100" s="134" t="n">
-        <v>8.869397968855964</v>
+        <v>8.869397968855965</v>
       </c>
       <c r="Z100" s="135" t="n">
-        <v>8.869397968855964</v>
+        <v>8.869397968855965</v>
       </c>
     </row>
     <row r="101">
@@ -33557,7 +33557,7 @@
         <v>111.9494145335249</v>
       </c>
       <c r="V103" s="139" t="n">
-        <v>95.18610366019895</v>
+        <v>95.18610366019897</v>
       </c>
       <c r="W103" s="140" t="n">
         <v>51.83334773437532</v>
@@ -33594,7 +33594,7 @@
         <v>353</v>
       </c>
       <c r="J104" s="142" t="n">
-        <v>132.727068836402</v>
+        <v>132.7270688364021</v>
       </c>
       <c r="K104" s="143" t="n">
         <v>99.96010795959765</v>
@@ -33606,7 +33606,7 @@
         <v>33.18867931990665</v>
       </c>
       <c r="N104" s="144" t="n">
-        <v>398.9186558156983</v>
+        <v>398.9186558156985</v>
       </c>
       <c r="P104" s="142" t="n">
         <v>173.280619982703</v>
